--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_by_Sample_Type.xlsx
@@ -867,10 +867,10 @@
         <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -893,10 +893,10 @@
         <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="H3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -919,10 +919,10 @@
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="5">
@@ -945,10 +945,10 @@
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7230544408811</v>
+        <v>11.7236546644519</v>
       </c>
       <c r="H5" t="n">
-        <v>1.38906066577268</v>
+        <v>1.38912905347294</v>
       </c>
     </row>
     <row r="6">
@@ -971,10 +971,10 @@
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>10.0799264008542</v>
+        <v>10.0802443137262</v>
       </c>
       <c r="H6" t="n">
-        <v>0.497528984762263</v>
+        <v>0.497542723654256</v>
       </c>
     </row>
     <row r="7">
@@ -997,10 +997,10 @@
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="H7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -1023,10 +1023,10 @@
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="H8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -1049,10 +1049,10 @@
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76893878922744</v>
+        <v>3.76987050415154</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0636877863152674</v>
+        <v>0.0637147014776062</v>
       </c>
     </row>
     <row r="10">
@@ -1075,10 +1075,10 @@
         <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.35711416912975</v>
+        <v>2.35719235917727</v>
       </c>
       <c r="H10" t="n">
-        <v>0.204291718921909</v>
+        <v>0.204302288466635</v>
       </c>
     </row>
     <row r="11">
@@ -1101,10 +1101,10 @@
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="H11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -1127,10 +1127,10 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>1.51390231586276</v>
+        <v>1.51398482750938</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0492796742344197</v>
+        <v>0.0492823020955965</v>
       </c>
     </row>
     <row r="13">
@@ -1153,10 +1153,10 @@
         <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>1.32056948721848</v>
+        <v>1.32060121834943</v>
       </c>
       <c r="H13" t="n">
-        <v>0.355227968619002</v>
+        <v>0.35523739701465</v>
       </c>
     </row>
     <row r="14">
@@ -1179,10 +1179,10 @@
         <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26562125220215</v>
+        <v>1.26569079615314</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0294564339085155</v>
+        <v>0.0294573793386389</v>
       </c>
     </row>
     <row r="15">
@@ -1205,10 +1205,10 @@
         <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="H15" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="16">
@@ -1231,10 +1231,10 @@
         <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="17">
@@ -1257,10 +1257,10 @@
         <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="H17" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="18">
@@ -1283,10 +1283,10 @@
         <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>0.592633978638086</v>
+        <v>0.592619268970162</v>
       </c>
       <c r="H18" t="n">
-        <v>0.213338796403032</v>
+        <v>0.213329511213247</v>
       </c>
     </row>
     <row r="19">
@@ -1309,10 +1309,10 @@
         <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>0.351175985734941</v>
+        <v>0.351322253471971</v>
       </c>
       <c r="H19" t="n">
-        <v>0.063645753435139</v>
+        <v>0.063670868567551</v>
       </c>
     </row>
     <row r="20">
@@ -1335,10 +1335,10 @@
         <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>0.334808283505506</v>
+        <v>0.334864889368922</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0213862302764069</v>
+        <v>0.0213890199646482</v>
       </c>
     </row>
     <row r="21">
@@ -1361,10 +1361,10 @@
         <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>0.315533179010191</v>
+        <v>0.315664450816511</v>
       </c>
       <c r="H21" t="n">
-        <v>0.137830515667426</v>
+        <v>0.137885777517319</v>
       </c>
     </row>
     <row r="22">
@@ -1387,10 +1387,10 @@
         <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>0.295145624389156</v>
+        <v>0.295190449716847</v>
       </c>
       <c r="H22" t="n">
-        <v>0.204404607400901</v>
+        <v>0.204437888414301</v>
       </c>
     </row>
     <row r="23">
@@ -1413,10 +1413,10 @@
         <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="H23" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="24">
@@ -1439,7 +1439,7 @@
         <v>73</v>
       </c>
       <c r="G24" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="H24"/>
     </row>
@@ -1463,10 +1463,10 @@
         <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>0.201693532470772</v>
+        <v>0.201728236934702</v>
       </c>
       <c r="H25" t="n">
-        <v>0.048108553541404</v>
+        <v>0.048105500208644</v>
       </c>
     </row>
     <row r="26">
@@ -1489,10 +1489,10 @@
         <v>76</v>
       </c>
       <c r="G26" t="n">
-        <v>0.15812321900899</v>
+        <v>0.158187424211174</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0798332359822568</v>
+        <v>0.0798625220540073</v>
       </c>
     </row>
     <row r="27">
@@ -1515,10 +1515,10 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>0.146974458714768</v>
+        <v>0.146966996070451</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0129045399311217</v>
+        <v>0.0129042651403242</v>
       </c>
     </row>
     <row r="28">
@@ -1541,10 +1541,10 @@
         <v>79</v>
       </c>
       <c r="G28" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="29">
@@ -1567,10 +1567,10 @@
         <v>80</v>
       </c>
       <c r="G29" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="H29" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="30">
@@ -1593,7 +1593,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="n">
-        <v>0.078814578864233</v>
+        <v>0.0788203573425972</v>
       </c>
       <c r="H30"/>
     </row>
@@ -1617,10 +1617,10 @@
         <v>86</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0767766031568904</v>
+        <v>0.0767885465735697</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00674044272963043</v>
+        <v>0.0067414249958013</v>
       </c>
     </row>
     <row r="32">
@@ -1643,10 +1643,10 @@
         <v>87</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="33">
@@ -1669,7 +1669,7 @@
         <v>91</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="H33"/>
     </row>
@@ -1693,10 +1693,10 @@
         <v>92</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0669521263651332</v>
+        <v>0.0669679113379792</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00894656365606824</v>
+        <v>0.00894835440130837</v>
       </c>
     </row>
     <row r="35">
@@ -1719,10 +1719,10 @@
         <v>93</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0625501941406329</v>
+        <v>0.0625693354883635</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0067821560765687</v>
+        <v>0.00678591990212035</v>
       </c>
     </row>
     <row r="36">
@@ -1745,7 +1745,7 @@
         <v>94</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0621202460293485</v>
+        <v>0.0621248227529827</v>
       </c>
       <c r="H36"/>
     </row>
@@ -1769,10 +1769,10 @@
         <v>95</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0577451720243945</v>
+        <v>0.0577727984075593</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00615561606809399</v>
+        <v>0.00615693902785514</v>
       </c>
     </row>
     <row r="38">
@@ -1795,10 +1795,10 @@
         <v>96</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0495380365661187</v>
+        <v>0.0495498540995747</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00736556453700803</v>
+        <v>0.00736707645047622</v>
       </c>
     </row>
     <row r="39">
@@ -1821,10 +1821,10 @@
         <v>97</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0459537638479654</v>
+        <v>0.0459740490217306</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0094901820429826</v>
+        <v>0.00949304968572704</v>
       </c>
     </row>
     <row r="40">
@@ -1847,10 +1847,10 @@
         <v>98</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0439933304196353</v>
+        <v>0.043986841089278</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0261664828828586</v>
+        <v>0.0261566748666346</v>
       </c>
     </row>
     <row r="41">
@@ -1873,10 +1873,10 @@
         <v>99</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0367236334629408</v>
+        <v>0.0367300028822527</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00554384650356856</v>
+        <v>0.00554647325349502</v>
       </c>
     </row>
     <row r="42">
@@ -1899,10 +1899,10 @@
         <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0365713646859972</v>
+        <v>0.0365853684413202</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00787153471918318</v>
+        <v>0.0078751496126478</v>
       </c>
     </row>
     <row r="43">
@@ -1925,7 +1925,7 @@
         <v>104</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="H43"/>
     </row>
@@ -1949,7 +1949,7 @@
         <v>105</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0259313943733403</v>
+        <v>0.0259343842821128</v>
       </c>
       <c r="H44"/>
     </row>
@@ -1973,7 +1973,7 @@
         <v>110</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="H45"/>
     </row>
@@ -1997,7 +1997,7 @@
         <v>111</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0221796909801125</v>
+        <v>0.0221801678579688</v>
       </c>
       <c r="H46"/>
     </row>
@@ -2021,10 +2021,10 @@
         <v>112</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0204826413821713</v>
+        <v>0.0204865591798642</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000426852181464751</v>
+        <v>0.000427153986817937</v>
       </c>
     </row>
     <row r="48">
@@ -2047,10 +2047,10 @@
         <v>113</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0163092206223587</v>
+        <v>0.0163086158082577</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00700928958906865</v>
+        <v>0.00701053084458542</v>
       </c>
     </row>
     <row r="49">
@@ -2073,10 +2073,10 @@
         <v>115</v>
       </c>
       <c r="G49" t="n">
-        <v>0.015787218129565</v>
+        <v>0.0157889711102967</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00588204337348365</v>
+        <v>0.00588424684009715</v>
       </c>
     </row>
     <row r="50">
@@ -2099,10 +2099,10 @@
         <v>116</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0157066434709264</v>
+        <v>0.0157129730732199</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00644455578850006</v>
+        <v>0.00644786593254792</v>
       </c>
     </row>
     <row r="51">
@@ -2125,10 +2125,10 @@
         <v>117</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0118024547022103</v>
+        <v>0.0118043788700566</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00691877303390335</v>
+        <v>0.00692066009538753</v>
       </c>
     </row>
     <row r="52">
@@ -2151,10 +2151,10 @@
         <v>118</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0115267247547719</v>
+        <v>0.0115291836987614</v>
       </c>
       <c r="H52" t="n">
-        <v>0.000846464203009839</v>
+        <v>0.000849967633715466</v>
       </c>
     </row>
     <row r="53">
@@ -2177,10 +2177,10 @@
         <v>119</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00822078116659366</v>
+        <v>0.00822619208734681</v>
       </c>
       <c r="H53" t="n">
-        <v>0.000909803377331876</v>
+        <v>0.000910625346116799</v>
       </c>
     </row>
     <row r="54">
@@ -2203,7 +2203,7 @@
         <v>120</v>
       </c>
       <c r="G54" t="n">
-        <v>0.00742521471180896</v>
+        <v>0.00743308436708383</v>
       </c>
       <c r="H54"/>
     </row>
@@ -2227,10 +2227,10 @@
         <v>121</v>
       </c>
       <c r="G55" t="n">
-        <v>0.00654430843040156</v>
+        <v>0.00654449193357052</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00215677517739025</v>
+        <v>0.00215414214857648</v>
       </c>
     </row>
     <row r="56">
@@ -2253,7 +2253,7 @@
         <v>122</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00579574385982276</v>
+        <v>0.00579642008713082</v>
       </c>
       <c r="H56"/>
     </row>
@@ -2277,10 +2277,10 @@
         <v>125</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00544138864064831</v>
+        <v>0.00544111302489999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00199442737963186</v>
+        <v>0.0019924666610927</v>
       </c>
     </row>
     <row r="58">
@@ -2303,7 +2303,7 @@
         <v>126</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00305750505737567</v>
+        <v>0.0030607072709903</v>
       </c>
       <c r="H58"/>
     </row>
@@ -2327,7 +2327,7 @@
         <v>127</v>
       </c>
       <c r="G59" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="H59"/>
     </row>
@@ -2351,7 +2351,7 @@
         <v>129</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="H60"/>
     </row>
@@ -2375,7 +2375,7 @@
         <v>130</v>
       </c>
       <c r="G61" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="H61"/>
     </row>
@@ -2399,7 +2399,7 @@
         <v>131</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="H62"/>
     </row>
@@ -2423,7 +2423,7 @@
         <v>132</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00183588926511166</v>
+        <v>0.00183521185829894</v>
       </c>
       <c r="H63"/>
     </row>
@@ -2447,7 +2447,7 @@
         <v>133</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00137691694883374</v>
+        <v>0.0013764088937242</v>
       </c>
       <c r="H64"/>
     </row>
@@ -2471,7 +2471,7 @@
         <v>134</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00131042119560235</v>
+        <v>0.00131166982510323</v>
       </c>
       <c r="H65"/>
     </row>
@@ -2495,7 +2495,7 @@
         <v>136</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00119930614215706</v>
+        <v>0.00119886362192086</v>
       </c>
       <c r="H66"/>
     </row>
@@ -2519,7 +2519,7 @@
         <v>137</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000817876104891649</v>
+        <v>0.000818656917912728</v>
       </c>
       <c r="H67"/>
     </row>
@@ -2580,10 +2580,10 @@
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>54.1129255454368</v>
+        <v>54.2903931518093</v>
       </c>
       <c r="H2" t="n">
-        <v>10.2494138186117</v>
+        <v>10.2900236788944</v>
       </c>
     </row>
     <row r="3">
@@ -2606,10 +2606,10 @@
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>5.60580054516845</v>
+        <v>5.56924494107659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.580672928149858</v>
+        <v>0.578594848887287</v>
       </c>
     </row>
     <row r="4">
@@ -2632,10 +2632,10 @@
         <v>95</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7854109959605</v>
+        <v>3.7776036435902</v>
       </c>
       <c r="H4" t="n">
-        <v>0.281556330293027</v>
+        <v>0.280887077483567</v>
       </c>
     </row>
     <row r="5">
@@ -2658,10 +2658,10 @@
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10115817741734</v>
+        <v>3.09351946137996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.223177430346691</v>
+        <v>0.222603641648086</v>
       </c>
     </row>
     <row r="6">
@@ -2684,10 +2684,10 @@
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>3.06739139740554</v>
+        <v>3.01882625814057</v>
       </c>
       <c r="H6" t="n">
-        <v>0.444867388771745</v>
+        <v>0.434510459085714</v>
       </c>
     </row>
     <row r="7">
@@ -2710,10 +2710,10 @@
         <v>134</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92515278313589</v>
+        <v>2.91614954708321</v>
       </c>
       <c r="H7" t="n">
-        <v>0.649023421214462</v>
+        <v>0.647024131365027</v>
       </c>
     </row>
     <row r="8">
@@ -2736,10 +2736,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83713058958943</v>
+        <v>2.82977723474855</v>
       </c>
       <c r="H8" t="n">
-        <v>0.275977363948369</v>
+        <v>0.275310440732123</v>
       </c>
     </row>
     <row r="9">
@@ -2762,10 +2762,10 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38068014178256</v>
+        <v>2.37341644833467</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0576789885094573</v>
+        <v>0.0575256732831891</v>
       </c>
     </row>
     <row r="10">
@@ -2788,10 +2788,10 @@
         <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3714300919777</v>
+        <v>2.36654661741218</v>
       </c>
       <c r="H10" t="n">
-        <v>0.619525480262922</v>
+        <v>0.618148293180579</v>
       </c>
     </row>
     <row r="11">
@@ -2814,10 +2814,10 @@
         <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>2.22646824760753</v>
+        <v>2.22052226455152</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0721958492944152</v>
+        <v>0.0719774092107668</v>
       </c>
     </row>
     <row r="12">
@@ -2840,10 +2840,10 @@
         <v>139</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18825280558799</v>
+        <v>2.18337154728828</v>
       </c>
       <c r="H12" t="n">
-        <v>0.354080883046388</v>
+        <v>0.353309227269523</v>
       </c>
     </row>
     <row r="13">
@@ -2866,10 +2866,10 @@
         <v>76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.79399390263439</v>
+        <v>1.78964468472146</v>
       </c>
       <c r="H13" t="n">
-        <v>0.173134219159752</v>
+        <v>0.172614049162021</v>
       </c>
     </row>
     <row r="14">
@@ -2892,10 +2892,10 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>1.59352579114758</v>
+        <v>1.59022548798454</v>
       </c>
       <c r="H14" t="n">
-        <v>0.103663931247931</v>
+        <v>0.103469674183492</v>
       </c>
     </row>
     <row r="15">
@@ -2918,10 +2918,10 @@
         <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>1.18493752733886</v>
+        <v>1.18200724744164</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0541441131746403</v>
+        <v>0.0539795998378335</v>
       </c>
     </row>
     <row r="16">
@@ -2944,10 +2944,10 @@
         <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.06970571227957</v>
+        <v>1.0674985661161</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0987684112129183</v>
+        <v>0.0985596005357212</v>
       </c>
     </row>
     <row r="17">
@@ -2970,10 +2970,10 @@
         <v>140</v>
       </c>
       <c r="G17" t="n">
-        <v>0.944839788116803</v>
+        <v>0.942081723387715</v>
       </c>
       <c r="H17" t="n">
-        <v>0.663800673244031</v>
+        <v>0.661848715635598</v>
       </c>
     </row>
     <row r="18">
@@ -2996,10 +2996,10 @@
         <v>119</v>
       </c>
       <c r="G18" t="n">
-        <v>0.78579338214919</v>
+        <v>0.783887360959518</v>
       </c>
       <c r="H18" t="n">
-        <v>0.212072620108389</v>
+        <v>0.211526772365095</v>
       </c>
     </row>
     <row r="19">
@@ -3022,10 +3022,10 @@
         <v>136</v>
       </c>
       <c r="G19" t="n">
-        <v>0.751673776876524</v>
+        <v>0.750074310901611</v>
       </c>
       <c r="H19" t="n">
-        <v>0.115842844679538</v>
+        <v>0.115409103286247</v>
       </c>
     </row>
     <row r="20">
@@ -3048,10 +3048,10 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.68762281206237</v>
+        <v>0.686220471624085</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0353025091401378</v>
+        <v>0.0352442767042614</v>
       </c>
     </row>
     <row r="21">
@@ -3074,10 +3074,10 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.631996283953237</v>
+        <v>0.63032116297978</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0848296824794338</v>
+        <v>0.0845859430110073</v>
       </c>
     </row>
     <row r="22">
@@ -3100,10 +3100,10 @@
         <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>0.609402834383088</v>
+        <v>0.607559817112255</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0917140243010207</v>
+        <v>0.0914162281307068</v>
       </c>
     </row>
     <row r="23">
@@ -3126,10 +3126,10 @@
         <v>118</v>
       </c>
       <c r="G23" t="n">
-        <v>0.539977725117721</v>
+        <v>0.538595239981787</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0990346529113007</v>
+        <v>0.0987490409188721</v>
       </c>
     </row>
     <row r="24">
@@ -3152,10 +3152,10 @@
         <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.509258253215987</v>
+        <v>0.508486644638778</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0463705023945219</v>
+        <v>0.0462714911307914</v>
       </c>
     </row>
     <row r="25">
@@ -3178,10 +3178,10 @@
         <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.472436605263314</v>
+        <v>0.471208840460065</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0252498087518886</v>
+        <v>0.0251731703736768</v>
       </c>
     </row>
     <row r="26">
@@ -3204,10 +3204,10 @@
         <v>141</v>
       </c>
       <c r="G26" t="n">
-        <v>0.409636692974062</v>
+        <v>0.408484508448496</v>
       </c>
       <c r="H26" t="n">
-        <v>0.285095673387055</v>
+        <v>0.284293167942401</v>
       </c>
     </row>
     <row r="27">
@@ -3230,10 +3230,10 @@
         <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>0.404812028855803</v>
+        <v>0.403648266437176</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0461923181201646</v>
+        <v>0.0460389067740179</v>
       </c>
     </row>
     <row r="28">
@@ -3256,10 +3256,10 @@
         <v>142</v>
       </c>
       <c r="G28" t="n">
-        <v>0.379540111341148</v>
+        <v>0.378386520203736</v>
       </c>
       <c r="H28" t="n">
-        <v>0.114159836244252</v>
+        <v>0.113814107423817</v>
       </c>
     </row>
     <row r="29">
@@ -3282,10 +3282,10 @@
         <v>109</v>
       </c>
       <c r="G29" t="n">
-        <v>0.351612305902911</v>
+        <v>0.351483052903812</v>
       </c>
       <c r="H29" t="n">
-        <v>0.155646830278538</v>
+        <v>0.155638374117642</v>
       </c>
     </row>
     <row r="30">
@@ -3308,10 +3308,10 @@
         <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.202909538947346</v>
+        <v>0.200269945495604</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0110467151095926</v>
+        <v>0.0107855099896259</v>
       </c>
     </row>
     <row r="31">
@@ -3334,10 +3334,10 @@
         <v>120</v>
       </c>
       <c r="G31" t="n">
-        <v>0.199096599026493</v>
+        <v>0.19870832289067</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0355065722706006</v>
+        <v>0.0354274607597798</v>
       </c>
     </row>
     <row r="32">
@@ -3360,10 +3360,10 @@
         <v>105</v>
       </c>
       <c r="G32" t="n">
-        <v>0.188469864245512</v>
+        <v>0.188166453338591</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0446875602886054</v>
+        <v>0.0446022633016332</v>
       </c>
     </row>
     <row r="33">
@@ -3386,10 +3386,10 @@
         <v>58</v>
       </c>
       <c r="G33" t="n">
-        <v>0.184600424536622</v>
+        <v>0.184646978486627</v>
       </c>
       <c r="H33" t="n">
-        <v>0.105182511063958</v>
+        <v>0.105209613305111</v>
       </c>
     </row>
     <row r="34">
@@ -3412,10 +3412,10 @@
         <v>143</v>
       </c>
       <c r="G34" t="n">
-        <v>0.165569545228014</v>
+        <v>0.16509046326691</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0369747586442778</v>
+        <v>0.0368734941322675</v>
       </c>
     </row>
     <row r="35">
@@ -3438,10 +3438,10 @@
         <v>97</v>
       </c>
       <c r="G35" t="n">
-        <v>0.160965807217555</v>
+        <v>0.160742048643318</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0497501907714708</v>
+        <v>0.0496702084364198</v>
       </c>
     </row>
     <row r="36">
@@ -3464,10 +3464,10 @@
         <v>81</v>
       </c>
       <c r="G36" t="n">
-        <v>0.155717096274642</v>
+        <v>0.155400234659348</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0184387591010114</v>
+        <v>0.0184899075924613</v>
       </c>
     </row>
     <row r="37">
@@ -3490,7 +3490,7 @@
         <v>91</v>
       </c>
       <c r="G37" t="n">
-        <v>0.122043620490263</v>
+        <v>0.121669959620492</v>
       </c>
       <c r="H37"/>
     </row>
@@ -3514,10 +3514,10 @@
         <v>113</v>
       </c>
       <c r="G38" t="n">
-        <v>0.121924155269431</v>
+        <v>0.121615139757575</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0216648964387619</v>
+        <v>0.0216032597935625</v>
       </c>
     </row>
     <row r="39">
@@ -3540,10 +3540,10 @@
         <v>144</v>
       </c>
       <c r="G39" t="n">
-        <v>0.108641234150494</v>
+        <v>0.108332475323173</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0560510711965439</v>
+        <v>0.0558746856048751</v>
       </c>
     </row>
     <row r="40">
@@ -3566,10 +3566,10 @@
         <v>86</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0920697866362894</v>
+        <v>0.0919688949401428</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00886151896540007</v>
+        <v>0.00885495882644109</v>
       </c>
     </row>
     <row r="41">
@@ -3592,10 +3592,10 @@
         <v>145</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0907373664588965</v>
+        <v>0.0905326740107778</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0283013603662189</v>
+        <v>0.0282198179618309</v>
       </c>
     </row>
     <row r="42">
@@ -3618,10 +3618,10 @@
         <v>117</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0662518702897044</v>
+        <v>0.0661514160638245</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0183038619772068</v>
+        <v>0.0182663856706906</v>
       </c>
     </row>
     <row r="43">
@@ -3644,10 +3644,10 @@
         <v>116</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0619488344962114</v>
+        <v>0.0618247112955291</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0110560745853875</v>
+        <v>0.0110221436623438</v>
       </c>
     </row>
     <row r="44">
@@ -3670,7 +3670,7 @@
         <v>146</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0433577185025902</v>
+        <v>0.043267840737029</v>
       </c>
       <c r="H44"/>
     </row>
@@ -3694,7 +3694,7 @@
         <v>121</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0318564306645255</v>
+        <v>0.0317476398519908</v>
       </c>
       <c r="H45"/>
     </row>
@@ -3718,10 +3718,10 @@
         <v>49</v>
       </c>
       <c r="G46" t="n">
-        <v>0.031028231306782</v>
+        <v>0.0309894801565336</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00584097358048779</v>
+        <v>0.00583147820982544</v>
       </c>
     </row>
     <row r="47">
@@ -3744,7 +3744,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0296149408341879</v>
+        <v>0.0295685255181075</v>
       </c>
       <c r="H47"/>
     </row>
@@ -3768,10 +3768,10 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0245626860204542</v>
+        <v>0.0245125083963238</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004710844758253</v>
+        <v>0.00470171081027407</v>
       </c>
     </row>
     <row r="49">
@@ -3794,10 +3794,10 @@
         <v>51</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0214075508501126</v>
+        <v>0.0213649759054163</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00582731581784547</v>
+        <v>0.00581331564038483</v>
       </c>
     </row>
     <row r="50">
@@ -3820,10 +3820,10 @@
         <v>147</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0186704942169552</v>
+        <v>0.0186231897055007</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00252459090075161</v>
+        <v>0.00252529410416329</v>
       </c>
     </row>
     <row r="51">
@@ -3846,10 +3846,10 @@
         <v>92</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0155881721537321</v>
+        <v>0.0155379119594608</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00994705038762322</v>
+        <v>0.00991097796433392</v>
       </c>
     </row>
     <row r="52">
@@ -3872,7 +3872,7 @@
         <v>148</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0128759833850278</v>
+        <v>0.0128581822408941</v>
       </c>
       <c r="H52"/>
     </row>
@@ -3896,10 +3896,10 @@
         <v>56</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0112981671212124</v>
+        <v>0.0112786167875188</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00220970538097561</v>
+        <v>0.00220594438459289</v>
       </c>
     </row>
     <row r="54">
@@ -3922,7 +3922,7 @@
         <v>72</v>
       </c>
       <c r="G54" t="n">
-        <v>0.010897695032061</v>
+        <v>0.0108696982802279</v>
       </c>
       <c r="H54"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>98</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0106513042310604</v>
+        <v>0.0106246445711313</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00394667617239376</v>
+        <v>0.00392632865631399</v>
       </c>
     </row>
     <row r="56">
@@ -3972,7 +3972,7 @@
         <v>149</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00934882496246897</v>
+        <v>0.00933920304772745</v>
       </c>
       <c r="H56"/>
     </row>
@@ -3996,10 +3996,10 @@
         <v>112</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00929879081918949</v>
+        <v>0.00926703512692556</v>
       </c>
       <c r="H57" t="n">
-        <v>0.000177671116384785</v>
+        <v>0.000177064363377237</v>
       </c>
     </row>
     <row r="58">
@@ -4022,10 +4022,10 @@
         <v>150</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00923741692971944</v>
+        <v>0.00922401194337059</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00402235872236607</v>
+        <v>0.00401191677495358</v>
       </c>
     </row>
     <row r="59">
@@ -4048,7 +4048,7 @@
         <v>125</v>
       </c>
       <c r="G59" t="n">
-        <v>0.00848451746553975</v>
+        <v>0.00846763661958161</v>
       </c>
       <c r="H59"/>
     </row>
@@ -4072,7 +4072,7 @@
         <v>129</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00774464876233345</v>
+        <v>0.00771820051894665</v>
       </c>
       <c r="H60"/>
     </row>
@@ -4096,7 +4096,7 @@
         <v>137</v>
       </c>
       <c r="G61" t="n">
-        <v>0.00754331853172178</v>
+        <v>0.00752023439553818</v>
       </c>
       <c r="H61"/>
     </row>
@@ -4120,10 +4120,10 @@
         <v>127</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00583449835796795</v>
+        <v>0.00581457334427824</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00177087319763251</v>
+        <v>0.00176482560441357</v>
       </c>
     </row>
     <row r="63">
@@ -4146,7 +4146,7 @@
         <v>151</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00576924508164322</v>
+        <v>0.00575925782256471</v>
       </c>
       <c r="H63"/>
     </row>
@@ -4170,10 +4170,10 @@
         <v>94</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0050350462515322</v>
+        <v>0.00502171753305094</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00212628576734443</v>
+        <v>0.00211629065507607</v>
       </c>
     </row>
     <row r="65">
@@ -4196,10 +4196,10 @@
         <v>96</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00424961962064797</v>
+        <v>0.00424194711405695</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0013051723023104</v>
+        <v>0.00130260770571623</v>
       </c>
     </row>
     <row r="66">
@@ -4222,10 +4222,10 @@
         <v>44</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0041750160272889</v>
+        <v>0.00416640871343739</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00180723739682924</v>
+        <v>0.00180506113275028</v>
       </c>
     </row>
     <row r="67">
@@ -4248,10 +4248,10 @@
         <v>115</v>
       </c>
       <c r="G67" t="n">
-        <v>0.00356565387673206</v>
+        <v>0.00355446836301152</v>
       </c>
       <c r="H67" t="n">
-        <v>0.000994705038762322</v>
+        <v>0.000992009054043805</v>
       </c>
     </row>
     <row r="68">
@@ -4274,7 +4274,7 @@
         <v>104</v>
       </c>
       <c r="G68" t="n">
-        <v>0.00336541783215633</v>
+        <v>0.00335957532414269</v>
       </c>
       <c r="H68"/>
     </row>
@@ -4298,7 +4298,7 @@
         <v>154</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00333010546463304</v>
+        <v>0.00331873303929328</v>
       </c>
       <c r="H69"/>
     </row>
@@ -4322,7 +4322,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00251404162474268</v>
+        <v>0.0025108092006458</v>
       </c>
       <c r="H70"/>
     </row>
@@ -4346,7 +4346,7 @@
         <v>156</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00214639511666921</v>
+        <v>0.00214104773829548</v>
       </c>
       <c r="H71"/>
     </row>
@@ -4370,7 +4370,7 @@
         <v>87</v>
       </c>
       <c r="G72" t="n">
-        <v>0.00161919639026515</v>
+        <v>0.0016136667785894</v>
       </c>
       <c r="H72"/>
     </row>
@@ -4394,7 +4394,7 @@
         <v>158</v>
       </c>
       <c r="G73" t="n">
-        <v>0.000961590582669442</v>
+        <v>0.000959892825720676</v>
       </c>
       <c r="H73"/>
     </row>
@@ -4418,7 +4418,7 @@
         <v>159</v>
       </c>
       <c r="G74" t="n">
-        <v>0.000454684033659048</v>
+        <v>0.000453626930754705</v>
       </c>
       <c r="H74"/>
     </row>
